--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARTIDA - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARTIDA - 27_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IP IRON NXR150 KS 2009 EM DIANTE 173497</t>
+          <t xml:space="preserve">INTERRUPTOR PARTIDA  IRON NXR150 KS 2009 EM DIANTE 173497 </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IP AUDAX NXR150 2006 A 2009</t>
+          <t>INTERRUPTOR PARTIDA  AUDAX NXR150 2006 A 2009</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IP TMAC FAZER YS250 2001 A 2015 TM071</t>
+          <t>INTERRUPTOR PARTIDA  TMAC FAZER YS250 2001 A 2015 TM071</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IP IRON TITAN CG150 2014 A 2021/ FAN160 2016 A 2018 46513</t>
+          <t>INTERRUPTOR PARTIDA IRON TITAN CG150 2014 A 2021/ FAN160 2016 A 2018 46513</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IP CONDOR XRE190 1104504</t>
+          <t>INTERRUPTOR PARTIDA  CONDOR XRE190 1104504</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IP CONDOR CBX250 TWISTER 1103224</t>
+          <t>INTERRUPTOR PARTIDA  CONDOR CBX250 TWISTER 1103224</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IP IRON YES125 2008 EM DIANTE 27437</t>
+          <t>INTERRUPTOR PARTIDA  IRON YES125 2008 EM DIANTE 27437</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IP MAGNETRON CB300</t>
+          <t>INTERRUPTOR PARTIDA  MAGNETRON CB300</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -628,24 +628,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0000010014899</t>
+          <t>7908180608227</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CP RT NXR160001489</t>
+          <t>INTERRUPTOR PARTIDA ZOUIL TITAN CG150 2015/ FA160 2016 A 2023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -653,12 +649,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7908885019984</t>
+          <t>7908305602222</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CL RT FAZER150 2016 A 2022/ FACTOR 150 001497</t>
+          <t>INTERRUPTOR PARTIDA MHX FAN TITAN150 2014 A 2015/ FAN160 RD-43809</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,7 +662,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -674,22 +674,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7899101751194</t>
+          <t>7899468003264</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IF ALLEN FALCON 2006 EM DIANTE 75119</t>
+          <t xml:space="preserve">INTERRUPTOR PARTIDA AUDAX XR250 TORNADO 2002 A 2005 </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7908180608227</t>
+          <t>7899248153912</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IP ZOUIL TITAN CG150 2015/ FA160 2016 A 2023</t>
+          <t>INTERRUPTOR PARTIDA CONDOR XR250 TORNADO 2006 A 2008 1103761</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -712,7 +712,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -720,24 +724,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7908305602222</t>
+          <t>618341657045</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IP MHX FAN TITAN150 2014 A 2015/ FAN160 RD-43809</t>
+          <t>INTERRUPTOR PARTIDA IRON NXR150 2008/ XR250 TORNADO ATÉ 2005 023572</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -745,22 +745,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7899468003264</t>
+          <t>7908429152214</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IP AUDAX XR250 TORNADO 2002 A 2005 </t>
+          <t>INTERRUPTOR PARTIDA XILLION PCX150 9798</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7899248153912</t>
+          <t>7908073725574</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IP CONDOR XR250 TORNADO 2006 A 2008 1103761</t>
+          <t>INTERRUPTOR PARTIDA SMARTFOX FAZER250 2006 A 2015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -783,11 +783,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -795,17 +791,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>618341657045</t>
+          <t>7777777777</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IP IRON NXR150 2008/ XR250 TORNADO ATÉ 2005 023572</t>
+          <t>INTERRUPTOR PARTIDA DIX YBR125 2009</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -816,24 +812,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7908429152214</t>
+          <t>7895099122428</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IP XILLION PCX150 9798</t>
+          <t>INTERRUPTOR PARTIDA IRON YBR125 ATÉ 2008 028353</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -841,12 +833,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>070341176351</t>
+          <t>602883768277</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IB IRON LEAD110 2010 A 2015/ ELITE125 2019 350539</t>
+          <t>INTERRUPTOR PARTIDA IRON NXR160 188979</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -862,12 +854,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7908073725574</t>
+          <t>602883768666</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IP SMARTFOX FAZER250 2006 A 2015</t>
+          <t>INTERRUPTOR PARTIDA IRON FAZER YS150 188957</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,7 +867,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -883,12 +879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7777777777</t>
+          <t>7899641886479</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IP DIX YBR125 2009</t>
+          <t>INTERRUPTOR PARTIDA VEDAMOTORS YBR125 2002 A 2009 501283</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -902,22 +898,22 @@
       <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7898540623123</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL RIIE CBX250 TWISTER 2001 A 2008 IP0024</t>
+          <t>INTERRUPTOR PARTIDA SCUDE NXR150 2009 10460007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -925,12 +921,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7895099122428</t>
+          <t>7895099125849</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IP IRON YBR125 ATÉ 2008 028353</t>
+          <t>INTERRUPTOR PARTIDA IRON CBX250 TWISTER ATÉ 045390</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -946,17 +942,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>602883768277</t>
+          <t>602883768284</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IP IRON NXR160 188979</t>
+          <t>INTERRUPTOR PARTIDA IRON CB250F TWISTER 188381</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -967,12 +963,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>000010014967</t>
+          <t>7898540623130</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL RIIE FAZE250 2005 A 2010 001496</t>
+          <t>INTERRUPTOR PARTIDA SCUD NXR150 2006 A 2008 KS 10460008</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -980,11 +976,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -992,22 +984,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>602883768666</t>
+          <t>7895099122374</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IP IRON FAZER YS150 188957</t>
+          <t>INTERRUPTOR PARTIDA IRON NXR150 2009 A 2015 ESD 28348</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1017,17 +1009,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7899641886479</t>
+          <t>7898508616761</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IP VEDAMOTORS YBR125 2002 A 2009 501283</t>
+          <t>INTERRUPTOR PARTIDA MAGNETRON XRE300 FLEX 2013 A 2015/ XRE300 2010 A 2015 90237110</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1038,12 +1030,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7898540623123</t>
+          <t>7899761404737</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IP SCUDE NXR150 2009 10460007</t>
+          <t>INTERRUPTOR PARTIDA MAGNETRON XRE300 2016 A 2018 90237430</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1059,12 +1051,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7895099125849</t>
+          <t>7899651804135</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IP IRON CBX250 TWISTER ATÉ 045390</t>
+          <t>INTERRUPTOR PARTIDA SCUD XRE300 10460022</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1080,20 +1072,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>602883768284</t>
+          <t>7895099122367</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IP IRON CB250F TWISTER 188381</t>
+          <t>INTERRUPTOR PARTIDA IRON NXR150 KS 2006 A 2008 28347</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7898540623130</t>
+          <t>7899468003363</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IP SCUD NXR150 2006 A 2008 KS 10460008</t>
+          <t xml:space="preserve">INTERRUPTOR PARTIDA TRILHA XRE300 2012 A 2015 </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1122,17 +1118,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7895099122374</t>
+          <t>7895099122459</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IP IRON NXR150 2009 A 2015 ESD 28348</t>
+          <t>INTERRUPTOR PARTIDA IRON CG TITAN150 2004 A 2008 ES 28356</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1147,17 +1143,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7898508616761</t>
+          <t>7895099122190</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IP MAGNETRON XRE300 FLEX 2013 A 2015/ XRE300 2010 A 2015 90237110</t>
+          <t>INTERRUPTOR PARTIDA IRON YBR125 ATÉ 2008 ED 027442</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1168,12 +1164,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7899761404737</t>
+          <t>7908180603352</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IP MAGNETRON XRE300 2016 A 2018 90237430</t>
+          <t>INTERRUPTOR PARTIDA ZOUIL TITAN CG FAN150 2011 A 2013 FLEX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1189,12 +1185,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7899651804135</t>
+          <t>602883768697</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IP SCUD XRE300 10460022</t>
+          <t>INTERRUPTOR PARTIDA IRON YBR125/ FACTOR125 2014 A 2016 188963</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1202,7 +1198,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7895099122367</t>
+          <t>618341657007</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IP IRON NXR150 KS 2006 A 2008 28347</t>
+          <t>INTERRUPTOR PARTIDA IRON CG TITAN FAN150-160 2018 A 2023 200530</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1235,20 +1235,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7899468003363</t>
+          <t>7895099122213</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">IP TRILHA XRE300 2012 A 2015 </t>
+          <t>INTERRUPTOR PARTIDA IRON YES125 2005 A 2007/ INTRUDER125</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1256,200 +1260,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7895099122459</t>
+          <t> </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IP IRON CG TITAN150 2004 A 2008 ES 28356</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>7895099122190</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>IP IRON YBR125 ATÉ 2008 ED 027442</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>618341656956</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CL IRON XTZ250 LANDER/ TENERE 2001 A 2015 200541</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>7908180603352</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>IP ZOUIL TITAN CG FAN150 2011 A 2013 FLEX</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>602883768697</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>IP IRON YBR125/ FACTOR125 2014 A 2016 188963</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>618341657007</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>IP IRON CG TITAN FAN150-160 2018 A 2023 200530</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7909201023104</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CL CONDOR CG TITAN FAN160 1104502</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7895099122213</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>IP IRON YES125 2005 A 2007/ INTRUDER125</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
           <t> </t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARTIDA - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARTIDA - 27_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -595,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,11 +592,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -662,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -687,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -712,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,7 +692,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -758,11 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -804,7 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -825,7 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -846,7 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -867,11 +812,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -892,7 +832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,7 +852,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -934,7 +872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -955,7 +892,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -976,7 +912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -997,11 +932,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1022,7 +952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1043,7 +972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1064,7 +992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1085,11 +1012,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1110,7 +1032,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1131,11 +1052,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1156,7 +1072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,7 +1092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1198,11 +1112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,11 +1132,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1248,11 +1152,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1260,16 +1159,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t> </t>
+          <t>7908253814661</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>INTERRUPTOR PARTIDA TMAC YBR125 2000 A 2001</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
